--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N26_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.70438850375998</v>
+        <v>9.701963131860998</v>
       </c>
       <c r="D2" t="n">
-        <v>59.39586503043666</v>
+        <v>9.651828067445958</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
